--- a/artfynd/A 31288-2024 artfynd.xlsx
+++ b/artfynd/A 31288-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820717</v>
+        <v>119820716</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443441</v>
+        <v>443439</v>
       </c>
       <c r="R3" t="n">
         <v>6881320</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820718</v>
+        <v>119820717</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443442</v>
+        <v>443441</v>
       </c>
       <c r="R4" t="n">
-        <v>6881318</v>
+        <v>6881320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820716</v>
+        <v>119820718</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443439</v>
+        <v>443442</v>
       </c>
       <c r="R5" t="n">
-        <v>6881320</v>
+        <v>6881318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 31288-2024 artfynd.xlsx
+++ b/artfynd/A 31288-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820716</v>
+        <v>119820717</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443439</v>
+        <v>443441</v>
       </c>
       <c r="R3" t="n">
         <v>6881320</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820717</v>
+        <v>119820716</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443441</v>
+        <v>443439</v>
       </c>
       <c r="R4" t="n">
         <v>6881320</v>

--- a/artfynd/A 31288-2024 artfynd.xlsx
+++ b/artfynd/A 31288-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>119820717</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820716</v>
+        <v>119820718</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443439</v>
+        <v>443442</v>
       </c>
       <c r="R4" t="n">
-        <v>6881320</v>
+        <v>6881318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820718</v>
+        <v>119820716</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>79131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443442</v>
+        <v>443439</v>
       </c>
       <c r="R5" t="n">
-        <v>6881318</v>
+        <v>6881320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 31288-2024 artfynd.xlsx
+++ b/artfynd/A 31288-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820717</v>
+        <v>119820718</v>
       </c>
       <c r="B3" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443441</v>
+        <v>443442</v>
       </c>
       <c r="R3" t="n">
-        <v>6881320</v>
+        <v>6881318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820718</v>
+        <v>119820717</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443442</v>
+        <v>443441</v>
       </c>
       <c r="R4" t="n">
-        <v>6881318</v>
+        <v>6881320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 31288-2024 artfynd.xlsx
+++ b/artfynd/A 31288-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820718</v>
+        <v>119820716</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443442</v>
+        <v>443439</v>
       </c>
       <c r="R3" t="n">
-        <v>6881318</v>
+        <v>6881320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820717</v>
+        <v>119820718</v>
       </c>
       <c r="B4" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443441</v>
+        <v>443442</v>
       </c>
       <c r="R4" t="n">
-        <v>6881320</v>
+        <v>6881318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820716</v>
+        <v>119820717</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443439</v>
+        <v>443441</v>
       </c>
       <c r="R5" t="n">
         <v>6881320</v>
